--- a/public/uploads/files/SampleFormat.xlsx
+++ b/public/uploads/files/SampleFormat.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>Item No.</t>
   </si>
@@ -89,6 +89,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Extend Warranty</t>
+  </si>
+  <si>
     <t>VGACTTTROLLEY</t>
   </si>
   <si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>Active</t>
+  </si>
+  <si>
+    <t>[{"year":2,"amount":1500},{"year":3,"amount":2000}]</t>
   </si>
   <si>
     <t>VGACCWINDZYTROL</t>
@@ -1140,10 +1146,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1204,31 +1210,34 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2">
         <v>1499</v>
@@ -1237,54 +1246,57 @@
         <v>1499</v>
       </c>
       <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>25</v>
-      </c>
       <c r="R2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="U2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3">
         <v>1190</v>
@@ -1293,28 +1305,28 @@
         <v>412</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
